--- a/artfynd/A 17515-2022 artfynd.xlsx
+++ b/artfynd/A 17515-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 17515-2022 artfynd.xlsx
+++ b/artfynd/A 17515-2022 artfynd.xlsx
@@ -1582,7 +1582,7 @@
         <v>68273296</v>
       </c>
       <c r="B9" t="n">
-        <v>86174</v>
+        <v>86178</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 17515-2022 artfynd.xlsx
+++ b/artfynd/A 17515-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,59 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>68273298</v>
+        <v>68273263</v>
       </c>
       <c r="B2" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5964</v>
+        <v>366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ullstämma syd - Obj 1069, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540394.4561450451</v>
+        <v>540372</v>
       </c>
       <c r="R2" t="n">
-        <v>6468267.628842914</v>
+        <v>6468453</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,24 +743,14 @@
           <t>2017-09-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-09-14</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ädellövskog, triviallövskog och barrskog</t>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,7 +759,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -806,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>68273263</v>
+        <v>68273716</v>
       </c>
       <c r="B3" t="n">
-        <v>90138</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -842,14 +812,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ullstämma syd - Obj 1069, Ög</t>
+          <t>Ullstämma syd - Obj 1074, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540372.0486420562</v>
+        <v>540229</v>
       </c>
       <c r="R3" t="n">
-        <v>6468453.177256132</v>
+        <v>6468421</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,24 +849,14 @@
           <t>2017-09-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-09-14</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På asplåga</t>
+          <t>Ädellövskog, triviallövskog och barrskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -930,12 +890,7 @@
         <v>68273621</v>
       </c>
       <c r="B4" t="n">
-        <v>85129</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87196</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -976,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540254.8330563924</v>
+        <v>540255</v>
       </c>
       <c r="R4" t="n">
-        <v>6468501.831683967</v>
+        <v>6468502</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,19 +964,9 @@
           <t>2017-09-14</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-09-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1057,15 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>68273774</v>
+        <v>68273296</v>
       </c>
       <c r="B5" t="n">
-        <v>90457</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87368</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1073,34 +1013,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2055</v>
+        <v>449</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olivinkremla</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Russula olivina</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Ruots. &amp; Vauras</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ullstämma syd - Obj 1070, Ög</t>
+          <t>Ullstämma syd - Obj 1069, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540279.5682371969</v>
+        <v>540394</v>
       </c>
       <c r="R5" t="n">
-        <v>6468345.172868158</v>
+        <v>6468268</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1130,21 +1070,11 @@
           <t>2017-09-14</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2017-09-14</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
           <t>Ädellövskog, triviallövskog och barrskog</t>
@@ -1156,7 +1086,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1179,59 +1108,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>68273264</v>
+        <v>68328978</v>
       </c>
       <c r="B6" t="n">
-        <v>87441</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>88424</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1669</v>
+        <v>1008</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grå vedslidskivling</t>
+          <t>Igelkottsröksvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Volvariella caesiotincta</t>
+          <t>Lycoperdon echinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P. D. Orton</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ullstämma syd - Obj 1069, Ög</t>
+          <t>Ullstämma Syd - Obj 1070, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540372.0486420562</v>
+        <v>540269</v>
       </c>
       <c r="R6" t="n">
-        <v>6468453.177256132</v>
+        <v>6468391</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1258,27 +1173,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2017-09-14</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2017-09-14</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-09</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På asplåga</t>
+          <t>Barrskog NV om Nain. Bestånd 1070 i Linköping kn skogsbruksplan.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1290,14 +1195,9 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>Rolf-Göran Carlsson</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>RGC17-059</t>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>blandskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1308,7 +1208,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Leif Andersson, Börje H Fagerlind</t>
+          <t>Rolf-Göran Carlsson, Tomas Fasth</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1319,15 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>68273777</v>
+        <v>68328974</v>
       </c>
       <c r="B7" t="n">
-        <v>85187</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89921</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,43 +1230,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3611</v>
+        <v>1668</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Silkesslidskivling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Volvariella bombycina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Schaeff. : Fr.) Singer</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ullstämma syd - Obj 1070, Ög</t>
+          <t>Ullstämma Syd - Obj 1070, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540336.1987297051</v>
+        <v>540269</v>
       </c>
       <c r="R7" t="n">
-        <v>6468462.780832193</v>
+        <v>6468391</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1398,27 +1284,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2017-09-14</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2017-09-14</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-09</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ädellövskog, triviallövskog och barrskog</t>
+          <t>Barrskog NV om Nain. Bestånd 1070 i Linköping kn skogsbruksplan.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1429,6 +1305,11 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>blandskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1438,7 +1319,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Leif Andersson, Börje H Fagerlind</t>
+          <t>Rolf-Göran Carlsson, Tomas Fasth</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1449,59 +1330,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>68273620</v>
+        <v>68273264</v>
       </c>
       <c r="B8" t="n">
-        <v>85187</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89922</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3611</v>
+        <v>1669</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Grå vedslidskivling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Volvariella caesiotincta</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>P. D. Orton</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ullstämma syd - Obj 1071, Ög</t>
+          <t>Ullstämma syd - Obj 1069, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540240.72503281</v>
+        <v>540372</v>
       </c>
       <c r="R8" t="n">
-        <v>6468493.29105656</v>
+        <v>6468453</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1531,24 +1407,14 @@
           <t>2017-09-14</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2017-09-14</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ädellövskog, triviallövskog och barrskog</t>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1559,6 +1425,16 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>RGC17-059</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1579,37 +1455,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>68273296</v>
+        <v>68273337</v>
       </c>
       <c r="B9" t="n">
-        <v>86178</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Dialog hos rapportör</t>
-        </is>
+        <v>87322</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>449</v>
+        <v>1988</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1619,10 +1490,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540394</v>
+        <v>540365</v>
       </c>
       <c r="R9" t="n">
-        <v>6468268</v>
+        <v>6468200</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1690,50 +1561,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>68273337</v>
+        <v>68273774</v>
       </c>
       <c r="B10" t="n">
-        <v>85253</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93014</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1988</v>
+        <v>2055</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Olivinkremla</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Russula olivina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Ruots. &amp; Vauras</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ullstämma syd - Obj 1069, Ög</t>
+          <t>Ullstämma syd - Obj 1070, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540365.1780073369</v>
+        <v>540280</v>
       </c>
       <c r="R10" t="n">
-        <v>6468200.152518532</v>
+        <v>6468345</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1763,21 +1629,11 @@
           <t>2017-09-14</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2017-09-14</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
           <t>Ädellövskog, triviallövskog och barrskog</t>
@@ -1789,6 +1645,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1811,15 +1668,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>68273299</v>
+        <v>68570926</v>
       </c>
       <c r="B11" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1827,34 +1679,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3298</v>
+        <v>2590</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ullstämma syd - Obj 1069, Ög</t>
+          <t>Ullstämma Syd - Obj 1069, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540353.9094354175</v>
+        <v>540371</v>
       </c>
       <c r="R11" t="n">
-        <v>6468324.941825558</v>
+        <v>6468264</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1881,27 +1733,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2017-09-14</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2017-09-14</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-09</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ädellövskog, triviallövskog och barrskog</t>
+          <t>Barrskog med inslag av löv</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1921,7 +1763,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Leif Andersson, Börje H Fagerlind</t>
+          <t>Rolf-Göran Carlsson, Tomas Fasth</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1932,15 +1774,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>68328978</v>
+        <v>68570975</v>
       </c>
       <c r="B12" t="n">
-        <v>86860</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1948,34 +1785,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1008</v>
+        <v>2667</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Igelkottsröksvamp</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycoperdon echinatum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ullstämma Syd - Obj 1070, Ög</t>
+          <t>Ullstämma Syd - Obj 1069, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540269.1128465957</v>
+        <v>540457</v>
       </c>
       <c r="R12" t="n">
-        <v>6468390.723183283</v>
+        <v>6468245</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2005,24 +1842,14 @@
           <t>2014-09-09</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2014-09-09</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Barrskog NV om Nain. Bestånd 1070 i Linköping kn skogsbruksplan.</t>
+          <t>Barrskog med inslag av löv</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2033,11 +1860,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>blandskog</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2058,15 +1880,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>68328987</v>
+        <v>68570974</v>
       </c>
       <c r="B13" t="n">
-        <v>89376</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2074,21 +1891,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4660</v>
+        <v>2671</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2098,10 +1915,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540387.8407045812</v>
+        <v>540457</v>
       </c>
       <c r="R13" t="n">
-        <v>6468297.475025577</v>
+        <v>6468245</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2131,24 +1948,14 @@
           <t>2014-09-09</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2014-09-09</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Barrskog NNV om Nain. Bestånd 1069 i Linköping km skogsbruksplan.</t>
+          <t>Barrskog med inslag av löv</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2159,11 +1966,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2173,7 +1975,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Tomas Fasth, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Tomas Fasth</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2184,37 +1986,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>68328974</v>
+        <v>68571009</v>
       </c>
       <c r="B14" t="n">
-        <v>87440</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1668</v>
+        <v>2671</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Silkesslidskivling</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Volvariella bombycina</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff. : Fr.) Singer</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2224,10 +2021,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540269.1128465957</v>
+        <v>540304</v>
       </c>
       <c r="R14" t="n">
-        <v>6468390.723183283</v>
+        <v>6468488</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2257,24 +2054,14 @@
           <t>2014-09-09</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2014-09-09</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Barrskog NV om Nain. Bestånd 1070 i Linköping kn skogsbruksplan.</t>
+          <t>Barrskog med inslag av löv</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2285,11 +2072,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>blandskog</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2310,15 +2092,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>68328986</v>
+        <v>68571030</v>
       </c>
       <c r="B15" t="n">
-        <v>89794</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2326,34 +2103,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5321</v>
+        <v>2818</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rigidoporus corticola</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Pouzar</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ullstämma Syd - Obj 1069, Ög</t>
+          <t>Ullstämma Syd - Obj 1071, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540387.8407045812</v>
+        <v>540221</v>
       </c>
       <c r="R15" t="n">
-        <v>6468297.475025577</v>
+        <v>6468505</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2383,24 +2160,14 @@
           <t>2014-09-09</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2014-09-09</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Barrskog NNV om Nain. Bestånd 1069 i Linköping km skogsbruksplan.</t>
+          <t>Barrskog med inslag av löv</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2411,11 +2178,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2425,7 +2187,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Tomas Fasth, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Tomas Fasth</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2436,15 +2198,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>68570926</v>
+        <v>101948320</v>
       </c>
       <c r="B16" t="n">
-        <v>94160</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2452,37 +2209,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2590</v>
+        <v>2818</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ullstämma Syd - Obj 1069, Ög</t>
+          <t>Sågen, Ullstämma, Landeryd, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540371.3563933482</v>
+        <v>540236</v>
       </c>
       <c r="R16" t="n">
-        <v>6468264.243151082</v>
+        <v>6468493</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2506,27 +2263,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2014-09-09</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2014-09-09</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Barrskog med inslag av löv</t>
+          <t>2022-06-29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2541,31 +2283,26 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson</t>
+          <t>David Ek</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Tomas Fasth</t>
+          <t>David Ek</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
+          <t>Linköpings kommuns naturvårdsprogram 2023</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>68571030</v>
+        <v>68273299</v>
       </c>
       <c r="B17" t="n">
-        <v>93158</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2573,34 +2310,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2818</v>
+        <v>3298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ullstämma Syd - Obj 1071, Ög</t>
+          <t>Ullstämma syd - Obj 1069, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540220.6252751743</v>
+        <v>540354</v>
       </c>
       <c r="R17" t="n">
-        <v>6468505.155637613</v>
+        <v>6468325</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2627,27 +2364,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2014-09-09</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2014-09-09</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-14</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Barrskog med inslag av löv</t>
+          <t>Ädellövskog, triviallövskog och barrskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2667,7 +2394,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Tomas Fasth</t>
+          <t>Rolf-Göran Carlsson, Leif Andersson, Börje H Fagerlind</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2678,50 +2405,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>68571009</v>
+        <v>68273620</v>
       </c>
       <c r="B18" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87247</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2671</v>
+        <v>3611</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ullstämma Syd - Obj 1070, Ög</t>
+          <t>Ullstämma syd - Obj 1071, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540303.8678074365</v>
+        <v>540241</v>
       </c>
       <c r="R18" t="n">
-        <v>6468488.164143176</v>
+        <v>6468493</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2748,27 +2479,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2014-09-09</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2014-09-09</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-14</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Barrskog med inslag av löv</t>
+          <t>Ädellövskog, triviallövskog och barrskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2788,7 +2509,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Tomas Fasth</t>
+          <t>Rolf-Göran Carlsson, Leif Andersson, Börje H Fagerlind</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2799,50 +2520,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>68571011</v>
+        <v>68273777</v>
       </c>
       <c r="B19" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>87247</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222771</v>
+        <v>3611</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ullstämma Syd - Obj 1070, Ög</t>
+          <t>Ullstämma syd - Obj 1070, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540303.8678074365</v>
+        <v>540336</v>
       </c>
       <c r="R19" t="n">
-        <v>6468488.164143176</v>
+        <v>6468463</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2869,27 +2594,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2014-09-09</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2014-09-09</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-14</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Barrskog med inslag av löv</t>
+          <t>Ädellövskog, triviallövskog och barrskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2909,7 +2624,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Tomas Fasth</t>
+          <t>Rolf-Göran Carlsson, Leif Andersson, Börje H Fagerlind</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2920,15 +2635,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>68273616</v>
+        <v>68328987</v>
       </c>
       <c r="B20" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2936,37 +2646,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>4660</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ullstämma syd - Obj 1071, Ög</t>
+          <t>Ullstämma Syd - Obj 1069, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540240.72503281</v>
+        <v>540388</v>
       </c>
       <c r="R20" t="n">
-        <v>6468493.29105656</v>
+        <v>6468297</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2990,27 +2700,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2017-09-14</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2017-09-14</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-09</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ädellövskog, triviallövskog och barrskog</t>
+          <t>Barrskog NNV om Nain. Bestånd 1069 i Linköping km skogsbruksplan.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3021,6 +2721,11 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3030,7 +2735,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Leif Andersson, Börje H Fagerlind</t>
+          <t>Tomas Fasth, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -3041,15 +2746,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>68571013</v>
+        <v>68328986</v>
       </c>
       <c r="B21" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>91966</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3057,34 +2757,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>5321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ullstämma Syd - Obj 1070, Ög</t>
+          <t>Ullstämma Syd - Obj 1069, Ög</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540303.8678074365</v>
+        <v>540388</v>
       </c>
       <c r="R21" t="n">
-        <v>6468488.164143176</v>
+        <v>6468297</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3114,24 +2814,14 @@
           <t>2014-09-09</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2014-09-09</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Barrskog med inslag av löv</t>
+          <t>Barrskog NNV om Nain. Bestånd 1069 i Linköping km skogsbruksplan.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3142,6 +2832,11 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3151,7 +2846,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Tomas Fasth</t>
+          <t>Tomas Fasth, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -3162,50 +2857,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>68571034</v>
+        <v>68273298</v>
       </c>
       <c r="B22" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222771</v>
+        <v>5964</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ullstämma Syd - Obj 1071, Ög</t>
+          <t>Ullstämma syd - Obj 1069, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540220.6252751743</v>
+        <v>540394</v>
       </c>
       <c r="R22" t="n">
-        <v>6468505.155637613</v>
+        <v>6468268</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3232,27 +2931,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2014-09-09</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2014-09-09</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-14</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Barrskog med inslag av löv</t>
+          <t>Ädellövskog, triviallövskog och barrskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3261,6 +2950,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3272,7 +2962,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Tomas Fasth</t>
+          <t>Rolf-Göran Carlsson, Leif Andersson, Börje H Fagerlind</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3283,15 +2973,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>68571036</v>
+        <v>109889971</v>
       </c>
       <c r="B23" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3299,37 +2984,47 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ullstämma Syd - Obj 1071, Ög</t>
+          <t>Sågen, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540220.6252751743</v>
+        <v>540137</v>
       </c>
       <c r="R23" t="n">
-        <v>6468505.155637613</v>
+        <v>6468497</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3353,27 +3048,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2014-09-09</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2014-09-09</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Barrskog med inslag av löv</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3388,66 +3078,57 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson</t>
+          <t>Louise Nilsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Tomas Fasth</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
-        </is>
-      </c>
+          <t>Louise Nilsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>68570925</v>
+        <v>68571038</v>
       </c>
       <c r="B24" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>101897</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>220075</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ullstämma Syd - Obj 1069, Ög</t>
+          <t>Ullstämma Syd - Obj 1071, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540344.4045024568</v>
+        <v>540221</v>
       </c>
       <c r="R24" t="n">
-        <v>6468277.612023043</v>
+        <v>6468505</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3477,19 +3158,9 @@
           <t>2014-09-09</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2014-09-09</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3525,15 +3196,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>101948320</v>
+        <v>68273616</v>
       </c>
       <c r="B25" t="n">
-        <v>93158</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3541,37 +3207,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sågen, Ullstämma, Landeryd, Ög</t>
+          <t>Ullstämma syd - Obj 1071, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540235.4680568795</v>
+        <v>540241</v>
       </c>
       <c r="R25" t="n">
-        <v>6468493.237347484</v>
+        <v>6468493</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3595,22 +3261,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-06-29</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-06-29</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-14</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ädellövskog, triviallövskog och barrskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3625,17 +3286,759 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>David Ek</t>
+          <t>Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>David Ek</t>
+          <t>Rolf-Göran Carlsson, Leif Andersson, Börje H Fagerlind</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>Linköpings kommuns naturvårdsprogram 2023</t>
+          <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>68570925</v>
+      </c>
+      <c r="B26" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Ullstämma Syd - Obj 1069, Ög</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>540344</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6468278</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Landeryd</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2014-09-09</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2014-09-09</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Barrskog med inslag av löv</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>68570968</v>
+      </c>
+      <c r="B27" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Ullstämma Syd - Obj 1069, Ög</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>540457</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6468245</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Landeryd</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2014-09-09</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2014-09-09</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Barrskog med inslag av löv</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>68571013</v>
+      </c>
+      <c r="B28" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Ullstämma Syd - Obj 1070, Ög</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>540304</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6468488</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Landeryd</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2014-09-09</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2014-09-09</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Barrskog med inslag av löv</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>68571036</v>
+      </c>
+      <c r="B29" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Ullstämma Syd - Obj 1071, Ög</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>540221</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6468505</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Landeryd</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2014-09-09</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2014-09-09</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Barrskog med inslag av löv</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>68571112</v>
+      </c>
+      <c r="B30" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Ullstämma Syd - Obj 1073, Ög</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>540044</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6468384</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Landeryd</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2014-09-09</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2014-09-09</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Barrskog med inslag av löv</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>68571011</v>
+      </c>
+      <c r="B31" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Ullstämma Syd - Obj 1070, Ög</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>540304</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6468488</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Landeryd</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2014-09-09</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2014-09-09</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Barrskog med inslag av löv</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>68571034</v>
+      </c>
+      <c r="B32" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Ullstämma Syd - Obj 1071, Ög</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>540221</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6468505</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Landeryd</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2014-09-09</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2014-09-09</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Barrskog med inslag av löv</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 17515-2022 artfynd.xlsx
+++ b/artfynd/A 17515-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68273263</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68273716</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -999,6 +1014,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68273621</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68273296</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1216,6 +1241,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68328978</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1327,6 +1357,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68328974</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1452,6 +1487,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68273264</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1558,6 +1598,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68273337</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1665,6 +1710,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68273774</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1771,6 +1821,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68570926</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1877,6 +1932,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68570975</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1983,6 +2043,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68570974</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2089,6 +2154,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68571009</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2195,6 +2265,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68571030</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2296,6 +2371,11 @@
           <t>Linköpings kommuns naturvårdsprogram 2023</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101948320</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2402,6 +2482,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68273299</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2517,6 +2602,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68273620</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2632,6 +2722,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68273777</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2743,6 +2838,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68328987</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2854,6 +2954,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68328986</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2970,6 +3075,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68273298</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3087,6 +3197,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109889971</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3193,6 +3308,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68571038</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3299,6 +3419,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68273616</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3405,6 +3530,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68570925</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3511,6 +3641,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68570968</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3617,6 +3752,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68571013</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3723,6 +3863,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68571036</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3829,6 +3974,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68571112</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3935,6 +4085,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68571011</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4041,8 +4196,46 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68571034</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>